--- a/main.xlsx
+++ b/main.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9191h\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9191h\Desktop\[중1] - 1학기 진도 사항\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23DEB372-2A4B-42A8-B7D4-4699E6D71372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008DC80C-79D0-44D6-A505-B8FCB227B989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="903" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="350">
   <si>
     <t>내용</t>
   </si>
@@ -1574,7 +1574,20 @@
     <t>1주차</t>
   </si>
   <si>
-    <t>(도서) 청소년을 위한 법학 에세이</t>
+    <t>(도서) 청소년을 위한 법학 에세이 '1장 법, 신에게서 인간에게로'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(도서) 청소년을 위한 법학 에세이 '2장 헌법, 민주주의의 탄생'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(도서) 청소년을 위한 법학 에세이 '3장 법은 인권을 향해 ~ 4장 2절 정의는 때로 목숨을 요구한다'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(도서) 청소년을 위한 법학 에세이 '4장 3절 양심의 이름으로 민중의 편에 서다 ~ 5장 법과 인간을 둘러싼 끝나지 않은 논쟁'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2643,7 +2656,7 @@
     <col min="2" max="2" width="5.5" style="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.5625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="87.375" style="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="74.25" style="20" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.6875" style="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.5" style="20" bestFit="1" customWidth="1"/>
@@ -3304,7 +3317,7 @@
       </c>
       <c r="D28" s="33"/>
       <c r="E28" s="34" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F28" s="35" t="s">
         <v>52</v>
@@ -3824,7 +3837,7 @@
       </c>
       <c r="D49" s="33"/>
       <c r="E49" s="34" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F49" s="35" t="s">
         <v>52</v>
@@ -4344,7 +4357,7 @@
       </c>
       <c r="D70" s="33"/>
       <c r="E70" s="34" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F70" s="35" t="s">
         <v>52</v>
